--- a/samples/示例导入.xlsx
+++ b/samples/示例导入.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,10 +434,15 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>picture</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>A+introduction</t>
         </is>
@@ -459,10 +464,15 @@
           <t>ES</t>
         </is>
       </c>
-      <c r="D2" t="b">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="E2" t="b">
+      <c r="F2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/samples/示例导入.xlsx
+++ b/samples/示例导入.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>A+introduction</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>src</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -474,6 +479,11 @@
       </c>
       <c r="F2" t="b">
         <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://example.invalid/01.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>
